--- a/docs/data-notes/핀앤필부산_데이터조사.xlsx
+++ b/docs/data-notes/핀앤필부산_데이터조사.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\홍민지\Desktop\새 폴더\donga\compiler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\홍민지\Desktop\새 폴더\donga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{079B036E-4BE4-4533-9B64-B7C6E26F37E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E29738-E537-4134-A18F-E43F4B9EE6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{FFD4A6C1-C66B-4C7E-BD26-6A6DB7395793}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>장소명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,10 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>04:30-20:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>절, 사찰</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,10 +201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1/1, 설당일, 추석당일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>평일(10:00-20:00), 주말(10:00-21:00)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -269,10 +261,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>08:00-16:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>월요일, 1/1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -286,6 +274,18 @@
   </si>
   <si>
     <t>미술관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개별 시설 확인 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04:30-19:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:00-17:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -792,7 +792,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.45">
@@ -829,7 +829,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1">
         <v>35.18835</v>
@@ -838,13 +838,13 @@
         <v>129.223544</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>16</v>
@@ -853,7 +853,7 @@
         <v>22</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.45">
@@ -861,7 +861,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1">
         <v>35.079484999999998</v>
@@ -876,13 +876,16 @@
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.45">
@@ -890,7 +893,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1">
         <v>35.196027999999998</v>
@@ -899,13 +902,13 @@
         <v>129.212964</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>16</v>
@@ -914,15 +917,15 @@
         <v>22</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1">
         <v>35.101636999999997</v>
@@ -931,13 +934,13 @@
         <v>129.12287000000001</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>16</v>
@@ -946,15 +949,15 @@
         <v>22</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
         <v>35.100929000000001</v>
@@ -963,7 +966,7 @@
         <v>129.03243499999999</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>20</v>
@@ -983,7 +986,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1">
         <v>35.284323999999998</v>
@@ -992,13 +995,13 @@
         <v>129.069772</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>16</v>
@@ -1012,7 +1015,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C11" s="1">
         <v>35.165851000000004</v>
@@ -1021,22 +1024,22 @@
         <v>129.13675000000001</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
